--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487016_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487016_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6202</v>
+        <v>3.9926</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4942</v>
+        <v>4.8666</v>
       </c>
       <c r="F2" t="n">
         <v>-0.874</v>
@@ -610,10 +610,10 @@
         <v>1.8481</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4107</v>
+        <v>-0.2169</v>
       </c>
       <c r="T2" t="n">
-        <v>0.612</v>
+        <v>-0.0156</v>
       </c>
       <c r="U2" t="n">
         <v>-0.2013</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. KALU</t>
+          <t>N. FERRER IGLESIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3213</v>
+        <v>1.1976</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1707</v>
+        <v>0.9103</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8494</v>
+        <v>0.2873</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4786</v>
+        <v>1.4578</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7104</v>
+        <v>1.5314</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.189</v>
+        <v>-0.0736</v>
       </c>
       <c r="J3" t="n">
-        <v>2.062</v>
+        <v>1.4334</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2332</v>
+        <v>1.9729</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8288</v>
+        <v>-0.5395</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.5405</v>
+        <v>0.0244</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5228</v>
+        <v>-0.4415</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.0177</v>
+        <v>0.4659</v>
       </c>
       <c r="P3" t="n">
-        <v>0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.2321</v>
+        <v>-0.2053</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8481</v>
+        <v>1.2321</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1801</v>
+        <v>-1.169</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7514</v>
+        <v>-0.3178</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5713</v>
+        <v>-0.8512999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0037</v>
+        <v>-0.1179</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4144</v>
+        <v>-0.1179</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. FERRER IGLESIA</t>
+          <t>E. KALU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8336</v>
+        <v>0.9736</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6352</v>
+        <v>1.6748</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1984</v>
+        <v>-0.7012</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4578</v>
+        <v>-0.4786</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5314</v>
+        <v>0.7104</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0736</v>
+        <v>-1.189</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4334</v>
+        <v>2.062</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9729</v>
+        <v>1.2332</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5395</v>
+        <v>0.8288</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0244</v>
+        <v>-2.5405</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4415</v>
+        <v>-0.5228</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4659</v>
+        <v>-2.0177</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2321</v>
+        <v>1.8481</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.533</v>
+        <v>-0.1675</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5928</v>
+        <v>0.2556</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9402</v>
+        <v>-0.4231</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1179</v>
+        <v>1.0037</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1179</v>
+        <v>0.4144</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4646</v>
+        <v>-0.4192</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.244</v>
+        <v>-0.1394</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2205</v>
+        <v>-0.2798</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3514</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1131</v>
+        <v>-0.0678</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2635</v>
+        <v>-0.1589</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1504</v>
+        <v>0.0911</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. CASTILLO CARRASCO</t>
+          <t>J. JUANOLA MADERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.4335</v>
+        <v>-1.0105</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.4213</v>
+        <v>-0.3008</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9878</v>
+        <v>-0.7097</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4479</v>
+        <v>4.7095</v>
       </c>
       <c r="H6" t="n">
-        <v>0.415</v>
+        <v>1.5733</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8629</v>
+        <v>3.1362</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.8563</v>
+        <v>6.5527</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0779</v>
+        <v>1.8172</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9342</v>
+        <v>4.7355</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4084</v>
+        <v>-1.8432</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3371</v>
+        <v>-0.2438</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0713</v>
+        <v>-1.5993</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.8214</v>
+        <v>-5.3389</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0267</v>
+        <v>-7.3923</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2053</v>
+        <v>2.0534</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3428</v>
+        <v>-0.9268999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7169</v>
+        <v>-0.2907</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3741</v>
+        <v>-0.6362</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1786</v>
+        <v>0.5458</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1786</v>
+        <v>0.8295</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2838</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. JUANOLA MADERA</t>
+          <t>J. CASTILLO CARRASCO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.946</v>
+        <v>-1.7076</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.851</v>
+        <v>-2.2508</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.095</v>
+        <v>0.5432</v>
       </c>
       <c r="G7" t="n">
-        <v>4.7095</v>
+        <v>-1.4479</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5733</v>
+        <v>0.415</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1362</v>
+        <v>-1.8629</v>
       </c>
       <c r="J7" t="n">
-        <v>6.5527</v>
+        <v>-1.8563</v>
       </c>
       <c r="K7" t="n">
-        <v>1.8172</v>
+        <v>0.0779</v>
       </c>
       <c r="L7" t="n">
-        <v>4.7355</v>
+        <v>-1.9342</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8432</v>
+        <v>0.4084</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2438</v>
+        <v>0.3371</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5993</v>
+        <v>0.0713</v>
       </c>
       <c r="P7" t="n">
-        <v>-5.3389</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q7" t="n">
-        <v>-7.3923</v>
+        <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0534</v>
+        <v>0.2053</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.8624</v>
+        <v>-0.6169</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8409</v>
+        <v>-0.5464</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0215</v>
+        <v>-0.0706</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5458</v>
+        <v>1.1786</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8295</v>
+        <v>1.1786</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1607</v>
+        <v>-2.098</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3855</v>
+        <v>2.8039</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.5462</v>
+        <v>-4.9019</v>
       </c>
       <c r="G8" t="n">
         <v>0.0544</v>
@@ -1078,13 +1078,13 @@
         <v>1.8481</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.299</v>
+        <v>-0.2362</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5192</v>
+        <v>-0.1008</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2203</v>
+        <v>-0.1354</v>
       </c>
       <c r="V8" t="n">
         <v>-2.5322</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4269</v>
+        <v>-2.9046</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1377</v>
+        <v>-0.2807</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5646</v>
+        <v>-2.6239</v>
       </c>
       <c r="G9" t="n">
         <v>0.2531</v>
@@ -1156,13 +1156,13 @@
         <v>0.2053</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.179</v>
+        <v>-0.6567</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0386</v>
+        <v>-0.3798</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2176</v>
+        <v>-0.2769</v>
       </c>
       <c r="V9" t="n">
         <v>-2.7063</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4401</v>
+        <v>-3.0852</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5668</v>
+        <v>-2.3304</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8733</v>
+        <v>-0.7548</v>
       </c>
       <c r="G10" t="n">
         <v>-1.981</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2189</v>
+        <v>-0.864</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.651</v>
+        <v>-0.4146</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5679</v>
+        <v>-0.4493</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2402</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3551</v>
+        <v>-3.7317</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0312</v>
+        <v>-2.5857</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3239</v>
+        <v>-1.146</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9668</v>
@@ -1312,13 +1312,13 @@
         <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3188</v>
+        <v>-0.6954</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8409</v>
+        <v>-0.3953</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4779</v>
+        <v>-0.3001</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8641</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.451800000000002</v>
+        <v>-8.792999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>1.709</v>
+        <v>2.367800000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-11.1607</v>
+        <v>-11.1608</v>
       </c>
       <c r="G12" t="n">
         <v>4.2495</v>
@@ -1390,13 +1390,13 @@
         <v>10.2671</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.276199999999999</v>
+        <v>-5.6173</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.0232</v>
+        <v>-2.3643</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.2529</v>
+        <v>-3.2531</v>
       </c>
       <c r="V12" t="n">
         <v>-3.3182</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. MIKHAILOV PALTARAK</t>
+          <t>X. TORRENT BAYÉ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2212</v>
+        <v>5.4139</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8675</v>
+        <v>5.2065</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3538</v>
+        <v>0.2075</v>
       </c>
       <c r="G13" t="n">
-        <v>3.7037</v>
+        <v>0.3535</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2929</v>
+        <v>-0.8404</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4107</v>
+        <v>1.194</v>
       </c>
       <c r="J13" t="n">
-        <v>4.9943</v>
+        <v>2.7362</v>
       </c>
       <c r="K13" t="n">
-        <v>4.6786</v>
+        <v>0.6847</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3157</v>
+        <v>2.0515</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2907</v>
+        <v>-2.3827</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.3857</v>
+        <v>-1.5252</v>
       </c>
       <c r="O13" t="n">
-        <v>0.095</v>
+        <v>-0.8575</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.616</v>
+        <v>1.2321</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.2855</v>
+        <v>-1.0267</v>
       </c>
       <c r="R13" t="n">
-        <v>2.6694</v>
+        <v>2.2588</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1336</v>
+        <v>0.2925</v>
       </c>
       <c r="T13" t="n">
-        <v>0.98</v>
+        <v>-0.0389</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1536</v>
+        <v>0.3314</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>3.5359</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1786</v>
+        <v>3.5359</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYÉ</t>
+          <t>M. MIKHAILOV PALTARAK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0366</v>
+        <v>4.4524</v>
       </c>
       <c r="E14" t="n">
-        <v>4.265</v>
+        <v>3.3444</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2284</v>
+        <v>1.1079</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3535</v>
+        <v>3.7037</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8404</v>
+        <v>3.2929</v>
       </c>
       <c r="I14" t="n">
-        <v>1.194</v>
+        <v>0.4107</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7362</v>
+        <v>4.9943</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6847</v>
+        <v>4.6786</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0515</v>
+        <v>0.3157</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3827</v>
+        <v>-1.2907</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5252</v>
+        <v>-1.3857</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8575</v>
+        <v>0.095</v>
       </c>
       <c r="P14" t="n">
-        <v>1.2321</v>
+        <v>-0.616</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0267</v>
+        <v>-3.2855</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2588</v>
+        <v>2.6694</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0849</v>
+        <v>1.3647</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9804</v>
+        <v>0.4569</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1045</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>3.5359</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>3.5359</v>
+        <v>1.1786</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7131</v>
+        <v>3.6266</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6477</v>
+        <v>3.0661</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0653</v>
+        <v>0.5605</v>
       </c>
       <c r="G15" t="n">
         <v>0.2893</v>
@@ -1624,13 +1624,13 @@
         <v>0.616</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1363</v>
+        <v>1.0499</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1122</v>
+        <v>0.5306</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0241</v>
+        <v>0.5192</v>
       </c>
       <c r="V15" t="n">
         <v>1.8768</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8707</v>
+        <v>2.7598</v>
       </c>
       <c r="E16" t="n">
-        <v>2.356</v>
+        <v>3.402</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4853</v>
+        <v>-0.6423</v>
       </c>
       <c r="G16" t="n">
         <v>0.3639</v>
@@ -1702,13 +1702,13 @@
         <v>2.6694</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.368</v>
+        <v>0.5211</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1857</v>
+        <v>-0.1397</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8177</v>
+        <v>0.6607</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5893</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3934</v>
+        <v>1.423</v>
       </c>
       <c r="E17" t="n">
         <v>1.2234</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1699</v>
+        <v>0.1996</v>
       </c>
       <c r="G17" t="n">
         <v>1.4472</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0538</v>
+        <v>-0.0242</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0538</v>
+        <v>-0.0242</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5056</v>
+        <v>0.2301</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2302</v>
+        <v>0.1882</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2755</v>
+        <v>0.0419</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5738</v>
@@ -1858,13 +1858,13 @@
         <v>0.616</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5479000000000001</v>
+        <v>0.1879</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3875</v>
+        <v>0.0309</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1604</v>
+        <v>0.157</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8455</v>
+        <v>-0.8106</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3286</v>
+        <v>-0.4332</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5169</v>
+        <v>-0.3774</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6277</v>
@@ -1936,13 +1936,13 @@
         <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7904</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3757</v>
+        <v>0.2711</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3798</v>
+        <v>0.5192</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1786</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. LAROUSSE</t>
+          <t>F. ADEBAYO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8744</v>
+        <v>-1.0881</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4852</v>
+        <v>-1.4007</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3892</v>
+        <v>0.3127</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.1458</v>
+        <v>-2.941</v>
       </c>
       <c r="H20" t="n">
-        <v>-5.6509</v>
+        <v>-1.2942</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5051</v>
+        <v>-1.6468</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3133</v>
+        <v>-0.2112</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.9311</v>
+        <v>0.0915</v>
       </c>
       <c r="L20" t="n">
-        <v>2.6178</v>
+        <v>-0.3027</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.8325</v>
+        <v>-2.7298</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7198</v>
+        <v>-1.3857</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1127</v>
+        <v>-1.3441</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4107</v>
+        <v>0.2053</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.2588</v>
       </c>
       <c r="R20" t="n">
-        <v>2.6694</v>
+        <v>2.4641</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4275</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>3.0643</v>
+        <v>0.3485</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3632</v>
+        <v>0.5784</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5668</v>
+        <v>0.7207</v>
       </c>
       <c r="W20" t="n">
-        <v>0.0225</v>
+        <v>0.7207</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1463</v>
+        <v>-2.3493</v>
       </c>
       <c r="E21" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.9634</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2289</v>
+        <v>-1.3858</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1187</v>
@@ -2092,13 +2092,13 @@
         <v>0.2053</v>
       </c>
       <c r="S21" t="n">
-        <v>2.2742</v>
+        <v>1.0712</v>
       </c>
       <c r="T21" t="n">
-        <v>1.7627</v>
+        <v>0.7167</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5115</v>
+        <v>0.3546</v>
       </c>
       <c r="V21" t="n">
         <v>-0.4805</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. ADEBAYO</t>
+          <t>C. LAROUSSE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4113</v>
+        <v>-2.8113</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2376</v>
+        <v>-2.4727</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1738</v>
+        <v>-0.3387</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.941</v>
+        <v>-4.1458</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2942</v>
+        <v>-5.6509</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6468</v>
+        <v>1.5051</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2112</v>
+        <v>-1.3133</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0915</v>
+        <v>-3.9311</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3027</v>
+        <v>2.6178</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.7298</v>
+        <v>-2.8325</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3857</v>
+        <v>-1.7198</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3441</v>
+        <v>-1.1127</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2053</v>
+        <v>0.4107</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.2588</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4641</v>
+        <v>2.6694</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3964</v>
+        <v>1.4906</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4883</v>
+        <v>1.0768</v>
       </c>
       <c r="U22" t="n">
-        <v>0.092</v>
+        <v>0.4137</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7207</v>
+        <v>-0.5668</v>
       </c>
       <c r="W22" t="n">
-        <v>0.7207</v>
+        <v>0.0225</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="23">
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>9.451899999999998</v>
+        <v>10.8465</v>
       </c>
       <c r="E23" t="n">
         <v>11.1606</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.709</v>
+        <v>-0.3140999999999998</v>
       </c>
       <c r="G23" t="n">
         <v>-4.2494</v>
       </c>
       <c r="H23" t="n">
-        <v>-7.379899999999999</v>
+        <v>-7.3799</v>
       </c>
       <c r="I23" t="n">
         <v>3.1306</v>
@@ -2224,10 +2224,10 @@
         <v>9.530100000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>1.0737</v>
+        <v>1.073700000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>8.456499999999998</v>
+        <v>8.4565</v>
       </c>
       <c r="M23" t="n">
         <v>-13.7796</v>
@@ -2248,13 +2248,13 @@
         <v>14.3737</v>
       </c>
       <c r="S23" t="n">
-        <v>6.2761</v>
+        <v>7.670999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>3.253</v>
+        <v>3.2529</v>
       </c>
       <c r="U23" t="n">
-        <v>3.0232</v>
+        <v>4.417800000000001</v>
       </c>
       <c r="V23" t="n">
         <v>3.318199999999999</v>
